--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,4633 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130746559</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>447697</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6784479</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130746553</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>447903</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6784473</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130746522</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>447866</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6784597</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130746558</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>447718</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6784468</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130746520</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>447846</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6784643</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130746493</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>447766</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6784433</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130746498</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>447886</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6784627</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130746562</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>447730</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6784717</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130746519</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>447826</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6784623</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130746524</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>447932</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6784551</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130746530</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>447855</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6784599</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130746551</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>447928</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6784508</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130746570</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>447857</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6784524</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130746500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>447888</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6784627</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130746499</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>447930</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6784568</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130746525</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>447933</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6784552</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130746554</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>447915</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6784490</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130746490</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58013</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>447888</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6784627</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130746546</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92199</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>447898</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6784612</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130746531</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>447932</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6784555</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130746556</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>447876</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6784529</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130746510</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>447718</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6784441</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130746564</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>447866</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6784648</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130746569</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>447856</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6784518</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130746518</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>447815</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6784612</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130746515</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>447716</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6784496</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130746521</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>447834</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6784604</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130746496</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>447817</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6784636</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130746528</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>447952</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6784545</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130746555</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>447906</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6784505</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130746523</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>447940</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6784589</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130746516</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>447725</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6784696</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130746497</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>447838</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6784644</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130746560</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>447685</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6784529</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130746565</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>447912</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6784599</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130746561</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>447711</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6784677</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130746506</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>447826</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6784573</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130746503</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>447933</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6784497</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130746511</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>447748</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6784472</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130746495</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57851</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>447746</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6784474</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130746566</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>447949</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6784550</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130746563</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>447832</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6784636</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130746505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>447906</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6784476</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130746526</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>447950</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6784549</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130746552</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Evertsbergsvägen öst, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>447914</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6784497</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -1180,41 +1180,40 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130746520</v>
+        <v>130746493</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1224,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447846</v>
+        <v>447766</v>
       </c>
       <c r="R7" t="n">
-        <v>6784643</v>
+        <v>6784433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1267,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,40 +1285,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746493</v>
+        <v>130746520</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1330,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447766</v>
+        <v>447846</v>
       </c>
       <c r="R8" t="n">
-        <v>6784433</v>
+        <v>6784643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1497,45 +1497,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746562</v>
+        <v>130746530</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447730</v>
+        <v>447855</v>
       </c>
       <c r="R10" t="n">
-        <v>6784717</v>
+        <v>6784599</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,6 +1585,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1701,54 +1711,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746524</v>
+        <v>130746562</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447932</v>
+        <v>447730</v>
       </c>
       <c r="R12" t="n">
-        <v>6784551</v>
+        <v>6784717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1790,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746530</v>
+        <v>130746524</v>
       </c>
       <c r="B13" t="n">
         <v>8451</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447855</v>
+        <v>447932</v>
       </c>
       <c r="R13" t="n">
-        <v>6784599</v>
+        <v>6784551</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746570</v>
+        <v>130746499</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,34 +2023,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447857</v>
+        <v>447930</v>
       </c>
       <c r="R15" t="n">
-        <v>6784524</v>
+        <v>6784568</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,40 +2222,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746499</v>
+        <v>130746525</v>
       </c>
       <c r="B17" t="n">
-        <v>57851</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2257,10 +2266,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447930</v>
+        <v>447933</v>
       </c>
       <c r="R17" t="n">
-        <v>6784568</v>
+        <v>6784552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,6 +2310,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2319,54 +2329,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746525</v>
+        <v>130746570</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447933</v>
+        <v>447857</v>
       </c>
       <c r="R18" t="n">
-        <v>6784552</v>
+        <v>6784524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,7 +2408,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,42 +2527,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746490</v>
+        <v>130746546</v>
       </c>
       <c r="B20" t="n">
-        <v>58013</v>
+        <v>92199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2570,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447888</v>
+        <v>447898</v>
       </c>
       <c r="R20" t="n">
-        <v>6784627</v>
+        <v>6784612</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,6 +2609,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2632,37 +2628,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746546</v>
+        <v>130746490</v>
       </c>
       <c r="B21" t="n">
-        <v>92199</v>
+        <v>58013</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2670,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447898</v>
+        <v>447888</v>
       </c>
       <c r="R21" t="n">
-        <v>6784612</v>
+        <v>6784627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2714,7 +2715,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746518</v>
+        <v>130746515</v>
       </c>
       <c r="B27" t="n">
         <v>8451</v>
@@ -3272,7 +3272,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447815</v>
+        <v>447716</v>
       </c>
       <c r="R27" t="n">
-        <v>6784612</v>
+        <v>6784496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746515</v>
+        <v>130746518</v>
       </c>
       <c r="B28" t="n">
         <v>8451</v>
@@ -3379,7 +3379,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447716</v>
+        <v>447815</v>
       </c>
       <c r="R28" t="n">
-        <v>6784496</v>
+        <v>6784612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3868,41 +3868,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130746523</v>
+        <v>130746497</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>57851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3912,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447940</v>
+        <v>447838</v>
       </c>
       <c r="R33" t="n">
-        <v>6784589</v>
+        <v>6784644</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,7 +3955,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3975,7 +3973,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130746516</v>
+        <v>130746523</v>
       </c>
       <c r="B34" t="n">
         <v>8451</v>
@@ -4019,10 +4017,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447725</v>
+        <v>447940</v>
       </c>
       <c r="R34" t="n">
-        <v>6784696</v>
+        <v>6784589</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,40 +4080,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130746497</v>
+        <v>130746516</v>
       </c>
       <c r="B35" t="n">
-        <v>57851</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4125,10 +4124,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447838</v>
+        <v>447725</v>
       </c>
       <c r="R35" t="n">
-        <v>6784644</v>
+        <v>6784696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,6 +4168,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4284,45 +4284,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746565</v>
+        <v>130746506</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447912</v>
+        <v>447826</v>
       </c>
       <c r="R37" t="n">
-        <v>6784599</v>
+        <v>6784573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,6 +4372,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4381,7 +4391,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746561</v>
+        <v>130746565</v>
       </c>
       <c r="B38" t="n">
         <v>79211</v>
@@ -4416,10 +4426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447711</v>
+        <v>447912</v>
       </c>
       <c r="R38" t="n">
-        <v>6784677</v>
+        <v>6784599</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,54 +4488,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746506</v>
+        <v>130746561</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447826</v>
+        <v>447711</v>
       </c>
       <c r="R39" t="n">
-        <v>6784573</v>
+        <v>6784677</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4692,54 +4692,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130746511</v>
+        <v>130746563</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447748</v>
+        <v>447832</v>
       </c>
       <c r="R41" t="n">
-        <v>6784472</v>
+        <v>6784636</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4771,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4799,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746495</v>
+        <v>130746566</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4810,42 +4800,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447746</v>
+        <v>447949</v>
       </c>
       <c r="R42" t="n">
-        <v>6784474</v>
+        <v>6784550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4904,10 +4886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746566</v>
+        <v>130746495</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4915,34 +4897,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447949</v>
+        <v>447746</v>
       </c>
       <c r="R43" t="n">
-        <v>6784550</v>
+        <v>6784474</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5001,45 +4991,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746563</v>
+        <v>130746511</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447832</v>
+        <v>447748</v>
       </c>
       <c r="R44" t="n">
-        <v>6784636</v>
+        <v>6784472</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -1497,54 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746530</v>
+        <v>130746562</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447855</v>
+        <v>447730</v>
       </c>
       <c r="R10" t="n">
-        <v>6784599</v>
+        <v>6784717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1576,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746519</v>
+        <v>130746524</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1638,7 +1628,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447826</v>
+        <v>447932</v>
       </c>
       <c r="R11" t="n">
-        <v>6784623</v>
+        <v>6784551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,45 +1701,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746562</v>
+        <v>130746530</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447730</v>
+        <v>447855</v>
       </c>
       <c r="R12" t="n">
-        <v>6784717</v>
+        <v>6784599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,6 +1789,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746524</v>
+        <v>130746519</v>
       </c>
       <c r="B13" t="n">
         <v>8451</v>
@@ -1842,7 +1842,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447932</v>
+        <v>447826</v>
       </c>
       <c r="R13" t="n">
-        <v>6784551</v>
+        <v>6784623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3452,41 +3452,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130746521</v>
+        <v>130746496</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3496,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447834</v>
+        <v>447817</v>
       </c>
       <c r="R29" t="n">
-        <v>6784604</v>
+        <v>6784636</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,7 +3539,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3559,40 +3557,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130746496</v>
+        <v>130746521</v>
       </c>
       <c r="B30" t="n">
-        <v>57851</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3602,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447817</v>
+        <v>447834</v>
       </c>
       <c r="R30" t="n">
-        <v>6784636</v>
+        <v>6784604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,6 +3645,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4284,54 +4284,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746506</v>
+        <v>130746565</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447826</v>
+        <v>447912</v>
       </c>
       <c r="R37" t="n">
-        <v>6784573</v>
+        <v>6784599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,7 +4363,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4391,7 +4381,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746565</v>
+        <v>130746561</v>
       </c>
       <c r="B38" t="n">
         <v>79211</v>
@@ -4426,10 +4416,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447912</v>
+        <v>447711</v>
       </c>
       <c r="R38" t="n">
-        <v>6784599</v>
+        <v>6784677</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,45 +4478,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746561</v>
+        <v>130746506</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447711</v>
+        <v>447826</v>
       </c>
       <c r="R39" t="n">
-        <v>6784677</v>
+        <v>6784573</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>130746559</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130746553</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,45 +1083,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130746558</v>
+        <v>130746520</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447718</v>
+        <v>447846</v>
       </c>
       <c r="R6" t="n">
-        <v>6784468</v>
+        <v>6784643</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1171,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1183,7 +1193,7 @@
         <v>130746493</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,54 +1295,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746520</v>
+        <v>130746558</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447846</v>
+        <v>447718</v>
       </c>
       <c r="R8" t="n">
-        <v>6784643</v>
+        <v>6784468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>130746498</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>130746562</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746524</v>
+        <v>130746519</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1628,7 +1628,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447932</v>
+        <v>447826</v>
       </c>
       <c r="R11" t="n">
-        <v>6784551</v>
+        <v>6784623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746530</v>
+        <v>130746524</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447855</v>
+        <v>447932</v>
       </c>
       <c r="R12" t="n">
-        <v>6784599</v>
+        <v>6784551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746519</v>
+        <v>130746530</v>
       </c>
       <c r="B13" t="n">
         <v>8451</v>
@@ -1842,7 +1842,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447826</v>
+        <v>447855</v>
       </c>
       <c r="R13" t="n">
-        <v>6784623</v>
+        <v>6784599</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>130746551</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>130746499</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130746500</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,54 +2222,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746525</v>
+        <v>130746570</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447933</v>
+        <v>447857</v>
       </c>
       <c r="R17" t="n">
-        <v>6784552</v>
+        <v>6784524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2301,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2329,10 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746570</v>
+        <v>130746554</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,16 +2348,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447857</v>
+        <v>447915</v>
       </c>
       <c r="R18" t="n">
-        <v>6784524</v>
+        <v>6784490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,6 +2401,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2426,37 +2420,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130746554</v>
+        <v>130746525</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447915</v>
+        <v>447933</v>
       </c>
       <c r="R19" t="n">
-        <v>6784490</v>
+        <v>6784552</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746546</v>
+        <v>130746531</v>
       </c>
       <c r="B20" t="n">
-        <v>92199</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,26 +2538,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447898</v>
+        <v>447932</v>
       </c>
       <c r="R20" t="n">
-        <v>6784612</v>
+        <v>6784555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,42 +2634,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746490</v>
+        <v>130746546</v>
       </c>
       <c r="B21" t="n">
-        <v>58013</v>
+        <v>92212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2671,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447888</v>
+        <v>447898</v>
       </c>
       <c r="R21" t="n">
-        <v>6784627</v>
+        <v>6784612</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,6 +2716,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2733,41 +2735,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130746531</v>
+        <v>130746490</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2777,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447932</v>
+        <v>447888</v>
       </c>
       <c r="R22" t="n">
-        <v>6784555</v>
+        <v>6784627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,7 +2822,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>130746556</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,45 +3044,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130746564</v>
+        <v>130746518</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447866</v>
+        <v>447815</v>
       </c>
       <c r="R25" t="n">
-        <v>6784648</v>
+        <v>6784612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,6 +3132,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,45 +3151,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130746569</v>
+        <v>130746515</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447856</v>
+        <v>447716</v>
       </c>
       <c r="R26" t="n">
-        <v>6784518</v>
+        <v>6784496</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,6 +3239,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3238,54 +3258,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746515</v>
+        <v>130746569</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447716</v>
+        <v>447856</v>
       </c>
       <c r="R27" t="n">
-        <v>6784496</v>
+        <v>6784518</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,7 +3337,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3345,54 +3355,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746518</v>
+        <v>130746564</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447815</v>
+        <v>447866</v>
       </c>
       <c r="R28" t="n">
-        <v>6784612</v>
+        <v>6784648</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,7 +3434,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>130746496</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130746555</v>
+        <v>130746497</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,34 +3782,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447906</v>
+        <v>447838</v>
       </c>
       <c r="R32" t="n">
-        <v>6784505</v>
+        <v>6784644</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130746497</v>
+        <v>130746555</v>
       </c>
       <c r="B33" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,42 +3887,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447838</v>
+        <v>447906</v>
       </c>
       <c r="R33" t="n">
-        <v>6784644</v>
+        <v>6784505</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4187,45 +4187,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130746560</v>
+        <v>130746506</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447685</v>
+        <v>447826</v>
       </c>
       <c r="R36" t="n">
-        <v>6784529</v>
+        <v>6784573</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,6 +4275,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4284,10 +4294,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746565</v>
+        <v>130746560</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,10 +4329,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447912</v>
+        <v>447685</v>
       </c>
       <c r="R37" t="n">
-        <v>6784599</v>
+        <v>6784529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,10 +4391,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746561</v>
+        <v>130746565</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4416,10 +4426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447711</v>
+        <v>447912</v>
       </c>
       <c r="R38" t="n">
-        <v>6784677</v>
+        <v>6784599</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,54 +4488,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746506</v>
+        <v>130746561</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447826</v>
+        <v>447711</v>
       </c>
       <c r="R39" t="n">
-        <v>6784573</v>
+        <v>6784677</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>130746563</v>
       </c>
       <c r="B41" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746566</v>
+        <v>130746495</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,34 +4800,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447949</v>
+        <v>447746</v>
       </c>
       <c r="R42" t="n">
-        <v>6784550</v>
+        <v>6784474</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4886,10 +4894,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746495</v>
+        <v>130746566</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,42 +4905,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447746</v>
+        <v>447949</v>
       </c>
       <c r="R43" t="n">
-        <v>6784474</v>
+        <v>6784550</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5315,7 +5315,7 @@
         <v>130746552</v>
       </c>
       <c r="B47" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>130746559</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130746553</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,54 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130746520</v>
+        <v>130746558</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447846</v>
+        <v>447718</v>
       </c>
       <c r="R6" t="n">
-        <v>6784643</v>
+        <v>6784468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,40 +1180,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130746493</v>
+        <v>130746520</v>
       </c>
       <c r="B7" t="n">
-        <v>57859</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1233,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447766</v>
+        <v>447846</v>
       </c>
       <c r="R7" t="n">
-        <v>6784433</v>
+        <v>6784643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,6 +1268,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746558</v>
+        <v>130746493</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1298,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447718</v>
+        <v>447766</v>
       </c>
       <c r="R8" t="n">
-        <v>6784468</v>
+        <v>6784433</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1395,7 @@
         <v>130746498</v>
       </c>
       <c r="B9" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,45 +1497,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746562</v>
+        <v>130746530</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447730</v>
+        <v>447855</v>
       </c>
       <c r="R10" t="n">
-        <v>6784717</v>
+        <v>6784599</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,6 +1585,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1808,54 +1818,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746530</v>
+        <v>130746562</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447855</v>
+        <v>447730</v>
       </c>
       <c r="R13" t="n">
-        <v>6784599</v>
+        <v>6784717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,7 +1897,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>130746551</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746499</v>
+        <v>130746500</v>
       </c>
       <c r="B15" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447930</v>
+        <v>447888</v>
       </c>
       <c r="R15" t="n">
-        <v>6784568</v>
+        <v>6784627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746500</v>
+        <v>130746499</v>
       </c>
       <c r="B16" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447888</v>
+        <v>447930</v>
       </c>
       <c r="R16" t="n">
-        <v>6784627</v>
+        <v>6784568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2225,7 @@
         <v>130746570</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>130746554</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746531</v>
+        <v>130746546</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>92213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,32 +2538,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2571,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447932</v>
+        <v>447898</v>
       </c>
       <c r="R20" t="n">
-        <v>6784555</v>
+        <v>6784612</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,37 +2628,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746546</v>
+        <v>130746490</v>
       </c>
       <c r="B21" t="n">
-        <v>92212</v>
+        <v>58022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2672,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447898</v>
+        <v>447888</v>
       </c>
       <c r="R21" t="n">
-        <v>6784612</v>
+        <v>6784627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,7 +2715,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2735,40 +2733,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130746490</v>
+        <v>130746531</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2778,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447888</v>
+        <v>447932</v>
       </c>
       <c r="R22" t="n">
-        <v>6784627</v>
+        <v>6784555</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,6 +2821,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>130746556</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,54 +3044,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130746518</v>
+        <v>130746564</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447815</v>
+        <v>447866</v>
       </c>
       <c r="R25" t="n">
-        <v>6784612</v>
+        <v>6784648</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,7 +3123,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3151,54 +3141,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130746515</v>
+        <v>130746569</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447716</v>
+        <v>447856</v>
       </c>
       <c r="R26" t="n">
-        <v>6784496</v>
+        <v>6784518</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,7 +3220,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3258,45 +3238,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746569</v>
+        <v>130746518</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447856</v>
+        <v>447815</v>
       </c>
       <c r="R27" t="n">
-        <v>6784518</v>
+        <v>6784612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,6 +3326,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3355,45 +3345,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746564</v>
+        <v>130746515</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447866</v>
+        <v>447716</v>
       </c>
       <c r="R28" t="n">
-        <v>6784648</v>
+        <v>6784496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,6 +3433,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3452,40 +3452,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130746496</v>
+        <v>130746521</v>
       </c>
       <c r="B29" t="n">
-        <v>57859</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3495,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447817</v>
+        <v>447834</v>
       </c>
       <c r="R29" t="n">
-        <v>6784636</v>
+        <v>6784604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,6 +3540,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3557,41 +3559,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130746521</v>
+        <v>130746496</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>57860</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3601,10 +3602,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447834</v>
+        <v>447817</v>
       </c>
       <c r="R30" t="n">
-        <v>6784604</v>
+        <v>6784636</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,7 +3646,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3771,40 +3771,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130746497</v>
+        <v>130746516</v>
       </c>
       <c r="B32" t="n">
-        <v>57859</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3814,10 +3815,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447838</v>
+        <v>447725</v>
       </c>
       <c r="R32" t="n">
-        <v>6784644</v>
+        <v>6784696</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,6 +3859,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3876,45 +3878,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130746555</v>
+        <v>130746523</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447906</v>
+        <v>447940</v>
       </c>
       <c r="R33" t="n">
-        <v>6784505</v>
+        <v>6784589</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3955,6 +3966,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3973,41 +3985,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130746523</v>
+        <v>130746497</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57860</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4017,10 +4028,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447940</v>
+        <v>447838</v>
       </c>
       <c r="R34" t="n">
-        <v>6784589</v>
+        <v>6784644</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,7 +4072,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4080,54 +4090,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130746516</v>
+        <v>130746555</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447725</v>
+        <v>447906</v>
       </c>
       <c r="R35" t="n">
-        <v>6784696</v>
+        <v>6784505</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,7 +4169,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4187,54 +4187,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130746506</v>
+        <v>130746560</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447826</v>
+        <v>447685</v>
       </c>
       <c r="R36" t="n">
-        <v>6784573</v>
+        <v>6784529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,7 +4266,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4294,10 +4284,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746560</v>
+        <v>130746565</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4329,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447685</v>
+        <v>447912</v>
       </c>
       <c r="R37" t="n">
-        <v>6784529</v>
+        <v>6784599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,10 +4381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746565</v>
+        <v>130746561</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4426,10 +4416,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447912</v>
+        <v>447711</v>
       </c>
       <c r="R38" t="n">
-        <v>6784599</v>
+        <v>6784677</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,45 +4478,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746561</v>
+        <v>130746506</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447711</v>
+        <v>447826</v>
       </c>
       <c r="R39" t="n">
-        <v>6784677</v>
+        <v>6784573</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130746563</v>
+        <v>130746495</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4703,34 +4703,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447832</v>
+        <v>447746</v>
       </c>
       <c r="R41" t="n">
-        <v>6784636</v>
+        <v>6784474</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4789,10 +4797,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746495</v>
+        <v>130746563</v>
       </c>
       <c r="B42" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,42 +4808,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447746</v>
+        <v>447832</v>
       </c>
       <c r="R42" t="n">
-        <v>6784474</v>
+        <v>6784636</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4897,7 +4897,7 @@
         <v>130746566</v>
       </c>
       <c r="B43" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>130746552</v>
       </c>
       <c r="B47" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>130746559</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130746553</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130746558</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>130746493</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>130746498</v>
       </c>
       <c r="B9" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,54 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746530</v>
+        <v>130746562</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447855</v>
+        <v>447730</v>
       </c>
       <c r="R10" t="n">
-        <v>6784599</v>
+        <v>6784717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1576,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1818,45 +1808,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746562</v>
+        <v>130746530</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447730</v>
+        <v>447855</v>
       </c>
       <c r="R13" t="n">
-        <v>6784717</v>
+        <v>6784599</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>130746551</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746500</v>
+        <v>130746570</v>
       </c>
       <c r="B15" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,42 +2023,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447888</v>
+        <v>447857</v>
       </c>
       <c r="R15" t="n">
-        <v>6784627</v>
+        <v>6784524</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746499</v>
+        <v>130746554</v>
       </c>
       <c r="B16" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,31 +2120,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2160,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447930</v>
+        <v>447915</v>
       </c>
       <c r="R16" t="n">
-        <v>6784568</v>
+        <v>6784490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,6 +2191,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2222,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746570</v>
+        <v>130746499</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,34 +2221,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447857</v>
+        <v>447930</v>
       </c>
       <c r="R17" t="n">
-        <v>6784524</v>
+        <v>6784568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2319,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746554</v>
+        <v>130746500</v>
       </c>
       <c r="B18" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,26 +2326,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2357,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447915</v>
+        <v>447888</v>
       </c>
       <c r="R18" t="n">
-        <v>6784490</v>
+        <v>6784627</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,7 +2402,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>130746546</v>
       </c>
       <c r="B20" t="n">
-        <v>92213</v>
+        <v>92214</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>130746490</v>
       </c>
       <c r="B21" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2840,45 +2840,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130746556</v>
+        <v>130746510</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447876</v>
+        <v>447718</v>
       </c>
       <c r="R23" t="n">
-        <v>6784529</v>
+        <v>6784441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,6 +2928,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2937,54 +2947,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130746510</v>
+        <v>130746556</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447718</v>
+        <v>447876</v>
       </c>
       <c r="R24" t="n">
-        <v>6784441</v>
+        <v>6784529</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,7 +3026,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>130746564</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>130746569</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,41 +3452,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130746521</v>
+        <v>130746496</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3496,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447834</v>
+        <v>447817</v>
       </c>
       <c r="R29" t="n">
-        <v>6784604</v>
+        <v>6784636</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,7 +3539,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3559,40 +3557,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130746496</v>
+        <v>130746521</v>
       </c>
       <c r="B30" t="n">
-        <v>57860</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3602,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447817</v>
+        <v>447834</v>
       </c>
       <c r="R30" t="n">
-        <v>6784636</v>
+        <v>6784604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,6 +3645,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3771,54 +3771,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130746516</v>
+        <v>130746555</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447725</v>
+        <v>447906</v>
       </c>
       <c r="R32" t="n">
-        <v>6784696</v>
+        <v>6784505</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,7 +3850,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3878,41 +3868,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130746523</v>
+        <v>130746497</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3922,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447940</v>
+        <v>447838</v>
       </c>
       <c r="R33" t="n">
-        <v>6784589</v>
+        <v>6784644</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3966,7 +3955,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3985,40 +3973,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130746497</v>
+        <v>130746523</v>
       </c>
       <c r="B34" t="n">
-        <v>57860</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4028,10 +4017,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447838</v>
+        <v>447940</v>
       </c>
       <c r="R34" t="n">
-        <v>6784644</v>
+        <v>6784589</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4072,6 +4061,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4090,45 +4080,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130746555</v>
+        <v>130746516</v>
       </c>
       <c r="B35" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447906</v>
+        <v>447725</v>
       </c>
       <c r="R35" t="n">
-        <v>6784505</v>
+        <v>6784696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,6 +4168,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>130746560</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>130746565</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>130746561</v>
       </c>
       <c r="B38" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>130746495</v>
       </c>
       <c r="B41" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4797,45 +4797,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746563</v>
+        <v>130746511</v>
       </c>
       <c r="B42" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447832</v>
+        <v>447748</v>
       </c>
       <c r="R42" t="n">
-        <v>6784636</v>
+        <v>6784472</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4876,6 +4885,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4894,10 +4904,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746566</v>
+        <v>130746563</v>
       </c>
       <c r="B43" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4929,10 +4939,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447949</v>
+        <v>447832</v>
       </c>
       <c r="R43" t="n">
-        <v>6784550</v>
+        <v>6784636</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,54 +5001,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746511</v>
+        <v>130746566</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447748</v>
+        <v>447949</v>
       </c>
       <c r="R44" t="n">
-        <v>6784472</v>
+        <v>6784550</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5080,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>130746552</v>
       </c>
       <c r="B47" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -879,45 +879,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746553</v>
+        <v>130746522</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447903</v>
+        <v>447866</v>
       </c>
       <c r="R4" t="n">
-        <v>6784473</v>
+        <v>6784597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,54 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130746522</v>
+        <v>130746553</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447866</v>
+        <v>447903</v>
       </c>
       <c r="R5" t="n">
-        <v>6784597</v>
+        <v>6784473</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1180,41 +1180,40 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130746520</v>
+        <v>130746493</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1224,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447846</v>
+        <v>447766</v>
       </c>
       <c r="R7" t="n">
-        <v>6784643</v>
+        <v>6784433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1267,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,40 +1285,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746493</v>
+        <v>130746520</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1330,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447766</v>
+        <v>447846</v>
       </c>
       <c r="R8" t="n">
-        <v>6784433</v>
+        <v>6784643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746519</v>
+        <v>130746524</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1628,7 +1628,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447826</v>
+        <v>447932</v>
       </c>
       <c r="R11" t="n">
-        <v>6784623</v>
+        <v>6784551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746524</v>
+        <v>130746530</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447932</v>
+        <v>447855</v>
       </c>
       <c r="R12" t="n">
-        <v>6784551</v>
+        <v>6784599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746530</v>
+        <v>130746519</v>
       </c>
       <c r="B13" t="n">
         <v>8451</v>
@@ -1842,7 +1842,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447855</v>
+        <v>447826</v>
       </c>
       <c r="R13" t="n">
-        <v>6784599</v>
+        <v>6784623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746570</v>
+        <v>130746499</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,34 +2023,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447857</v>
+        <v>447930</v>
       </c>
       <c r="R15" t="n">
-        <v>6784524</v>
+        <v>6784568</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746554</v>
+        <v>130746500</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,26 +2128,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2147,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447915</v>
+        <v>447888</v>
       </c>
       <c r="R16" t="n">
-        <v>6784490</v>
+        <v>6784627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2191,7 +2204,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2210,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746499</v>
+        <v>130746570</v>
       </c>
       <c r="B17" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,42 +2233,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447930</v>
+        <v>447857</v>
       </c>
       <c r="R17" t="n">
-        <v>6784568</v>
+        <v>6784524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,10 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746500</v>
+        <v>130746554</v>
       </c>
       <c r="B18" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2326,31 +2330,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447888</v>
+        <v>447915</v>
       </c>
       <c r="R18" t="n">
-        <v>6784627</v>
+        <v>6784490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,6 +2401,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3044,45 +3044,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130746564</v>
+        <v>130746515</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447866</v>
+        <v>447716</v>
       </c>
       <c r="R25" t="n">
-        <v>6784648</v>
+        <v>6784496</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,6 +3132,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,45 +3151,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130746569</v>
+        <v>130746518</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447856</v>
+        <v>447815</v>
       </c>
       <c r="R26" t="n">
-        <v>6784518</v>
+        <v>6784612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,6 +3239,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3238,54 +3258,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746518</v>
+        <v>130746564</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447815</v>
+        <v>447866</v>
       </c>
       <c r="R27" t="n">
-        <v>6784612</v>
+        <v>6784648</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,7 +3337,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3345,54 +3355,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746515</v>
+        <v>130746569</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447716</v>
+        <v>447856</v>
       </c>
       <c r="R28" t="n">
-        <v>6784496</v>
+        <v>6784518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,7 +3434,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130746495</v>
+        <v>130746563</v>
       </c>
       <c r="B41" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4703,42 +4703,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447746</v>
+        <v>447832</v>
       </c>
       <c r="R41" t="n">
-        <v>6784474</v>
+        <v>6784636</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4797,54 +4789,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746511</v>
+        <v>130746566</v>
       </c>
       <c r="B42" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447748</v>
+        <v>447949</v>
       </c>
       <c r="R42" t="n">
-        <v>6784472</v>
+        <v>6784550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4885,7 +4868,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4904,10 +4886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746563</v>
+        <v>130746495</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4915,34 +4897,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447832</v>
+        <v>447746</v>
       </c>
       <c r="R43" t="n">
-        <v>6784636</v>
+        <v>6784474</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5001,45 +4991,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746566</v>
+        <v>130746511</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447949</v>
+        <v>447748</v>
       </c>
       <c r="R44" t="n">
-        <v>6784550</v>
+        <v>6784472</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -879,54 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746522</v>
+        <v>130746553</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447866</v>
+        <v>447903</v>
       </c>
       <c r="R4" t="n">
-        <v>6784597</v>
+        <v>6784473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +958,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,45 +976,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130746553</v>
+        <v>130746522</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447903</v>
+        <v>447866</v>
       </c>
       <c r="R5" t="n">
-        <v>6784473</v>
+        <v>6784597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1064,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1180,40 +1180,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130746493</v>
+        <v>130746520</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1223,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447766</v>
+        <v>447846</v>
       </c>
       <c r="R7" t="n">
-        <v>6784433</v>
+        <v>6784643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,6 +1268,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1285,41 +1287,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746520</v>
+        <v>130746493</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1329,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447846</v>
+        <v>447766</v>
       </c>
       <c r="R8" t="n">
-        <v>6784643</v>
+        <v>6784433</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1497,45 +1497,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746562</v>
+        <v>130746524</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447730</v>
+        <v>447932</v>
       </c>
       <c r="R10" t="n">
-        <v>6784717</v>
+        <v>6784551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,6 +1585,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1594,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746524</v>
+        <v>130746530</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1638,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447932</v>
+        <v>447855</v>
       </c>
       <c r="R11" t="n">
-        <v>6784551</v>
+        <v>6784599</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746530</v>
+        <v>130746519</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1735,7 +1745,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447855</v>
+        <v>447826</v>
       </c>
       <c r="R12" t="n">
-        <v>6784599</v>
+        <v>6784623</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,54 +1818,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746519</v>
+        <v>130746562</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447826</v>
+        <v>447730</v>
       </c>
       <c r="R13" t="n">
-        <v>6784623</v>
+        <v>6784717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,7 +1897,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746500</v>
+        <v>130746570</v>
       </c>
       <c r="B16" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,42 +2128,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447888</v>
+        <v>447857</v>
       </c>
       <c r="R16" t="n">
-        <v>6784627</v>
+        <v>6784524</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746570</v>
+        <v>130746554</v>
       </c>
       <c r="B17" t="n">
         <v>79221</v>
@@ -2251,16 +2243,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447857</v>
+        <v>447915</v>
       </c>
       <c r="R17" t="n">
-        <v>6784524</v>
+        <v>6784490</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,6 +2296,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2319,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746554</v>
+        <v>130746500</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,26 +2326,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2357,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447915</v>
+        <v>447888</v>
       </c>
       <c r="R18" t="n">
-        <v>6784490</v>
+        <v>6784627</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,7 +2402,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,37 +2527,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746546</v>
+        <v>130746490</v>
       </c>
       <c r="B20" t="n">
-        <v>92214</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447898</v>
+        <v>447888</v>
       </c>
       <c r="R20" t="n">
-        <v>6784612</v>
+        <v>6784627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,7 +2614,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2628,40 +2632,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746490</v>
+        <v>130746531</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2671,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447888</v>
+        <v>447932</v>
       </c>
       <c r="R21" t="n">
-        <v>6784627</v>
+        <v>6784555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,6 +2720,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130746531</v>
+        <v>130746546</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>92214</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,32 +2750,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447932</v>
+        <v>447898</v>
       </c>
       <c r="R22" t="n">
-        <v>6784555</v>
+        <v>6784612</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,54 +2840,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130746510</v>
+        <v>130746556</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447718</v>
+        <v>447876</v>
       </c>
       <c r="R23" t="n">
-        <v>6784441</v>
+        <v>6784529</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,7 +2919,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2947,45 +2937,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130746556</v>
+        <v>130746510</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447876</v>
+        <v>447718</v>
       </c>
       <c r="R24" t="n">
-        <v>6784529</v>
+        <v>6784441</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,6 +3025,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3044,54 +3044,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130746515</v>
+        <v>130746564</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447716</v>
+        <v>447866</v>
       </c>
       <c r="R25" t="n">
-        <v>6784496</v>
+        <v>6784648</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,7 +3123,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3151,54 +3141,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130746518</v>
+        <v>130746569</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447815</v>
+        <v>447856</v>
       </c>
       <c r="R26" t="n">
-        <v>6784612</v>
+        <v>6784518</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,7 +3220,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3258,45 +3238,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746564</v>
+        <v>130746515</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447866</v>
+        <v>447716</v>
       </c>
       <c r="R27" t="n">
-        <v>6784648</v>
+        <v>6784496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,6 +3326,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3355,45 +3345,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746569</v>
+        <v>130746518</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447856</v>
+        <v>447815</v>
       </c>
       <c r="R28" t="n">
-        <v>6784518</v>
+        <v>6784612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,6 +3433,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4187,45 +4187,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130746560</v>
+        <v>130746506</v>
       </c>
       <c r="B36" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447685</v>
+        <v>447826</v>
       </c>
       <c r="R36" t="n">
-        <v>6784529</v>
+        <v>6784573</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,6 +4275,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4284,7 +4294,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746565</v>
+        <v>130746560</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4319,10 +4329,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447912</v>
+        <v>447685</v>
       </c>
       <c r="R37" t="n">
-        <v>6784599</v>
+        <v>6784529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,7 +4391,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746561</v>
+        <v>130746565</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4416,10 +4426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447711</v>
+        <v>447912</v>
       </c>
       <c r="R38" t="n">
-        <v>6784677</v>
+        <v>6784599</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,54 +4488,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746506</v>
+        <v>130746561</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447826</v>
+        <v>447711</v>
       </c>
       <c r="R39" t="n">
-        <v>6784573</v>
+        <v>6784677</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130746563</v>
+        <v>130746495</v>
       </c>
       <c r="B41" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4703,34 +4703,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447832</v>
+        <v>447746</v>
       </c>
       <c r="R41" t="n">
-        <v>6784636</v>
+        <v>6784474</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4789,45 +4797,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746566</v>
+        <v>130746511</v>
       </c>
       <c r="B42" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447949</v>
+        <v>447748</v>
       </c>
       <c r="R42" t="n">
-        <v>6784550</v>
+        <v>6784472</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4868,6 +4885,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4886,10 +4904,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746495</v>
+        <v>130746563</v>
       </c>
       <c r="B43" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,42 +4915,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447746</v>
+        <v>447832</v>
       </c>
       <c r="R43" t="n">
-        <v>6784474</v>
+        <v>6784636</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,54 +5001,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746511</v>
+        <v>130746566</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447748</v>
+        <v>447949</v>
       </c>
       <c r="R44" t="n">
-        <v>6784472</v>
+        <v>6784550</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5080,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -4797,54 +4797,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746511</v>
+        <v>130746563</v>
       </c>
       <c r="B42" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447748</v>
+        <v>447832</v>
       </c>
       <c r="R42" t="n">
-        <v>6784472</v>
+        <v>6784636</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4885,7 +4876,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4904,7 +4894,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746563</v>
+        <v>130746566</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -4939,10 +4929,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447832</v>
+        <v>447949</v>
       </c>
       <c r="R43" t="n">
-        <v>6784636</v>
+        <v>6784550</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5001,45 +4991,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746566</v>
+        <v>130746511</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447949</v>
+        <v>447748</v>
       </c>
       <c r="R44" t="n">
-        <v>6784550</v>
+        <v>6784472</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130746558</v>
+        <v>130746493</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447718</v>
+        <v>447766</v>
       </c>
       <c r="R6" t="n">
-        <v>6784468</v>
+        <v>6784433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746493</v>
+        <v>130746558</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,42 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447766</v>
+        <v>447718</v>
       </c>
       <c r="R8" t="n">
-        <v>6784433</v>
+        <v>6784468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1497,54 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746524</v>
+        <v>130746562</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447932</v>
+        <v>447730</v>
       </c>
       <c r="R10" t="n">
-        <v>6784551</v>
+        <v>6784717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1576,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746530</v>
+        <v>130746519</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1638,7 +1628,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447855</v>
+        <v>447826</v>
       </c>
       <c r="R11" t="n">
-        <v>6784599</v>
+        <v>6784623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746519</v>
+        <v>130746524</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1745,7 +1735,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447826</v>
+        <v>447932</v>
       </c>
       <c r="R12" t="n">
-        <v>6784623</v>
+        <v>6784551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,45 +1808,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746562</v>
+        <v>130746530</v>
       </c>
       <c r="B13" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447730</v>
+        <v>447855</v>
       </c>
       <c r="R13" t="n">
-        <v>6784717</v>
+        <v>6784599</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746499</v>
+        <v>130746570</v>
       </c>
       <c r="B15" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,42 +2023,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447930</v>
+        <v>447857</v>
       </c>
       <c r="R15" t="n">
-        <v>6784568</v>
+        <v>6784524</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,7 +2109,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746570</v>
+        <v>130746554</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2146,16 +2138,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447857</v>
+        <v>447915</v>
       </c>
       <c r="R16" t="n">
-        <v>6784524</v>
+        <v>6784490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,6 +2191,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2214,37 +2210,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746554</v>
+        <v>130746525</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447915</v>
+        <v>447933</v>
       </c>
       <c r="R17" t="n">
-        <v>6784490</v>
+        <v>6784552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746500</v>
+        <v>130746499</v>
       </c>
       <c r="B18" t="n">
         <v>57861</v>
@@ -2358,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447888</v>
+        <v>447930</v>
       </c>
       <c r="R18" t="n">
-        <v>6784627</v>
+        <v>6784568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,41 +2422,40 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130746525</v>
+        <v>130746500</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2464,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447933</v>
+        <v>447888</v>
       </c>
       <c r="R19" t="n">
-        <v>6784552</v>
+        <v>6784627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,7 +2509,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2527,42 +2527,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746490</v>
+        <v>130746546</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>92214</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2570,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447888</v>
+        <v>447898</v>
       </c>
       <c r="R20" t="n">
-        <v>6784627</v>
+        <v>6784612</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,6 +2609,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2632,41 +2628,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746531</v>
+        <v>130746490</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2676,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447932</v>
+        <v>447888</v>
       </c>
       <c r="R21" t="n">
-        <v>6784555</v>
+        <v>6784627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,7 +2715,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2739,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130746546</v>
+        <v>130746531</v>
       </c>
       <c r="B22" t="n">
-        <v>92214</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,26 +2744,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447898</v>
+        <v>447932</v>
       </c>
       <c r="R22" t="n">
-        <v>6784612</v>
+        <v>6784555</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746515</v>
+        <v>130746518</v>
       </c>
       <c r="B27" t="n">
         <v>8451</v>
@@ -3272,7 +3272,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447716</v>
+        <v>447815</v>
       </c>
       <c r="R27" t="n">
-        <v>6784496</v>
+        <v>6784612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746518</v>
+        <v>130746515</v>
       </c>
       <c r="B28" t="n">
         <v>8451</v>
@@ -3379,7 +3379,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447815</v>
+        <v>447716</v>
       </c>
       <c r="R28" t="n">
-        <v>6784612</v>
+        <v>6784496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3452,40 +3452,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130746496</v>
+        <v>130746521</v>
       </c>
       <c r="B29" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3495,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447817</v>
+        <v>447834</v>
       </c>
       <c r="R29" t="n">
-        <v>6784636</v>
+        <v>6784604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,6 +3540,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3557,41 +3559,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130746521</v>
+        <v>130746496</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3601,10 +3602,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447834</v>
+        <v>447817</v>
       </c>
       <c r="R30" t="n">
-        <v>6784604</v>
+        <v>6784636</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,7 +3646,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130746555</v>
+        <v>130746497</v>
       </c>
       <c r="B32" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,34 +3782,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447906</v>
+        <v>447838</v>
       </c>
       <c r="R32" t="n">
-        <v>6784505</v>
+        <v>6784644</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130746497</v>
+        <v>130746555</v>
       </c>
       <c r="B33" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,42 +3887,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447838</v>
+        <v>447906</v>
       </c>
       <c r="R33" t="n">
-        <v>6784644</v>
+        <v>6784505</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4187,54 +4187,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130746506</v>
+        <v>130746560</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447826</v>
+        <v>447685</v>
       </c>
       <c r="R36" t="n">
-        <v>6784573</v>
+        <v>6784529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,7 +4266,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4294,7 +4284,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746560</v>
+        <v>130746565</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4329,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447685</v>
+        <v>447912</v>
       </c>
       <c r="R37" t="n">
-        <v>6784529</v>
+        <v>6784599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,7 +4381,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746565</v>
+        <v>130746561</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4426,10 +4416,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447912</v>
+        <v>447711</v>
       </c>
       <c r="R38" t="n">
-        <v>6784599</v>
+        <v>6784677</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,45 +4478,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746561</v>
+        <v>130746506</v>
       </c>
       <c r="B39" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447711</v>
+        <v>447826</v>
       </c>
       <c r="R39" t="n">
-        <v>6784677</v>
+        <v>6784573</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4797,45 +4797,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746563</v>
+        <v>130746511</v>
       </c>
       <c r="B42" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447832</v>
+        <v>447748</v>
       </c>
       <c r="R42" t="n">
-        <v>6784636</v>
+        <v>6784472</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4876,6 +4885,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4894,7 +4904,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746566</v>
+        <v>130746563</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -4929,10 +4939,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447949</v>
+        <v>447832</v>
       </c>
       <c r="R43" t="n">
-        <v>6784550</v>
+        <v>6784636</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,54 +5001,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746511</v>
+        <v>130746566</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447748</v>
+        <v>447949</v>
       </c>
       <c r="R44" t="n">
-        <v>6784472</v>
+        <v>6784550</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,7 +5080,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -1188,54 +1188,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130746520</v>
+        <v>130746558</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447846</v>
+        <v>447718</v>
       </c>
       <c r="R7" t="n">
-        <v>6784643</v>
+        <v>6784468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1267,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,45 +1285,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746558</v>
+        <v>130746520</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447718</v>
+        <v>447846</v>
       </c>
       <c r="R8" t="n">
-        <v>6784468</v>
+        <v>6784643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1373,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746519</v>
+        <v>130746524</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1628,7 +1628,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447826</v>
+        <v>447932</v>
       </c>
       <c r="R11" t="n">
-        <v>6784623</v>
+        <v>6784551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746524</v>
+        <v>130746530</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447932</v>
+        <v>447855</v>
       </c>
       <c r="R12" t="n">
-        <v>6784551</v>
+        <v>6784599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746530</v>
+        <v>130746519</v>
       </c>
       <c r="B13" t="n">
         <v>8451</v>
@@ -1842,7 +1842,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447855</v>
+        <v>447826</v>
       </c>
       <c r="R13" t="n">
-        <v>6784599</v>
+        <v>6784623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2527,37 +2527,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746546</v>
+        <v>130746490</v>
       </c>
       <c r="B20" t="n">
-        <v>92214</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447898</v>
+        <v>447888</v>
       </c>
       <c r="R20" t="n">
-        <v>6784612</v>
+        <v>6784627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,7 +2614,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2628,40 +2632,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746490</v>
+        <v>130746531</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2671,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447888</v>
+        <v>447932</v>
       </c>
       <c r="R21" t="n">
-        <v>6784627</v>
+        <v>6784555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,6 +2720,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130746531</v>
+        <v>130746546</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>92214</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,32 +2750,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447932</v>
+        <v>447898</v>
       </c>
       <c r="R22" t="n">
-        <v>6784555</v>
+        <v>6784612</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,45 +2840,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130746556</v>
+        <v>130746510</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447876</v>
+        <v>447718</v>
       </c>
       <c r="R23" t="n">
-        <v>6784529</v>
+        <v>6784441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,6 +2928,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2937,54 +2947,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130746510</v>
+        <v>130746556</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447718</v>
+        <v>447876</v>
       </c>
       <c r="R24" t="n">
-        <v>6784441</v>
+        <v>6784529</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,7 +3026,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3044,45 +3044,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130746564</v>
+        <v>130746518</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447866</v>
+        <v>447815</v>
       </c>
       <c r="R25" t="n">
-        <v>6784648</v>
+        <v>6784612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,6 +3132,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130746569</v>
+        <v>130746564</v>
       </c>
       <c r="B26" t="n">
         <v>79221</v>
@@ -3176,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447856</v>
+        <v>447866</v>
       </c>
       <c r="R26" t="n">
-        <v>6784518</v>
+        <v>6784648</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,54 +3248,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746518</v>
+        <v>130746569</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447815</v>
+        <v>447856</v>
       </c>
       <c r="R27" t="n">
-        <v>6784612</v>
+        <v>6784518</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,7 +3327,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3452,41 +3452,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130746521</v>
+        <v>130746496</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3496,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447834</v>
+        <v>447817</v>
       </c>
       <c r="R29" t="n">
-        <v>6784604</v>
+        <v>6784636</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,7 +3539,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3559,40 +3557,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130746496</v>
+        <v>130746521</v>
       </c>
       <c r="B30" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3602,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447817</v>
+        <v>447834</v>
       </c>
       <c r="R30" t="n">
-        <v>6784636</v>
+        <v>6784604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,6 +3645,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4797,54 +4797,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746511</v>
+        <v>130746563</v>
       </c>
       <c r="B42" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447748</v>
+        <v>447832</v>
       </c>
       <c r="R42" t="n">
-        <v>6784472</v>
+        <v>6784636</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4885,7 +4876,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4904,7 +4894,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746563</v>
+        <v>130746566</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -4939,10 +4929,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447832</v>
+        <v>447949</v>
       </c>
       <c r="R43" t="n">
-        <v>6784636</v>
+        <v>6784550</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5001,45 +4991,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746566</v>
+        <v>130746511</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447949</v>
+        <v>447748</v>
       </c>
       <c r="R44" t="n">
-        <v>6784550</v>
+        <v>6784472</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,6 +5079,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -879,45 +879,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746553</v>
+        <v>130746522</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447903</v>
+        <v>447866</v>
       </c>
       <c r="R4" t="n">
-        <v>6784473</v>
+        <v>6784597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,54 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130746522</v>
+        <v>130746553</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447866</v>
+        <v>447903</v>
       </c>
       <c r="R5" t="n">
-        <v>6784597</v>
+        <v>6784473</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130746493</v>
+        <v>130746558</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,42 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447766</v>
+        <v>447718</v>
       </c>
       <c r="R6" t="n">
-        <v>6784433</v>
+        <v>6784468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,45 +1180,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130746558</v>
+        <v>130746520</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447718</v>
+        <v>447846</v>
       </c>
       <c r="R7" t="n">
-        <v>6784468</v>
+        <v>6784643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,6 +1268,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1285,41 +1287,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746520</v>
+        <v>130746493</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1329,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447846</v>
+        <v>447766</v>
       </c>
       <c r="R8" t="n">
-        <v>6784643</v>
+        <v>6784433</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2012,45 +2012,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746570</v>
+        <v>130746525</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447857</v>
+        <v>447933</v>
       </c>
       <c r="R15" t="n">
-        <v>6784524</v>
+        <v>6784552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,6 +2100,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2109,7 +2119,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746554</v>
+        <v>130746570</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2138,19 +2148,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447915</v>
+        <v>447857</v>
       </c>
       <c r="R16" t="n">
-        <v>6784490</v>
+        <v>6784524</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2191,7 +2198,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2210,43 +2216,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746525</v>
+        <v>130746554</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447933</v>
+        <v>447915</v>
       </c>
       <c r="R17" t="n">
-        <v>6784552</v>
+        <v>6784490</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,40 +2527,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746490</v>
+        <v>130746531</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2570,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447888</v>
+        <v>447932</v>
       </c>
       <c r="R20" t="n">
-        <v>6784627</v>
+        <v>6784555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,6 +2615,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746531</v>
+        <v>130746546</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>92222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,32 +2645,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2676,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447932</v>
+        <v>447898</v>
       </c>
       <c r="R21" t="n">
-        <v>6784555</v>
+        <v>6784612</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,37 +2735,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130746546</v>
+        <v>130746490</v>
       </c>
       <c r="B22" t="n">
-        <v>92214</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2777,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447898</v>
+        <v>447888</v>
       </c>
       <c r="R22" t="n">
-        <v>6784612</v>
+        <v>6784627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,7 +2822,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2840,54 +2840,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130746510</v>
+        <v>130746556</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447718</v>
+        <v>447876</v>
       </c>
       <c r="R23" t="n">
-        <v>6784441</v>
+        <v>6784529</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,7 +2919,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2947,45 +2937,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130746556</v>
+        <v>130746510</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447876</v>
+        <v>447718</v>
       </c>
       <c r="R24" t="n">
-        <v>6784529</v>
+        <v>6784441</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,6 +3025,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3044,54 +3044,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130746518</v>
+        <v>130746564</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447815</v>
+        <v>447866</v>
       </c>
       <c r="R25" t="n">
-        <v>6784612</v>
+        <v>6784648</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,7 +3123,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3151,7 +3141,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130746564</v>
+        <v>130746569</v>
       </c>
       <c r="B26" t="n">
         <v>79221</v>
@@ -3186,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447866</v>
+        <v>447856</v>
       </c>
       <c r="R26" t="n">
-        <v>6784648</v>
+        <v>6784518</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,45 +3238,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746569</v>
+        <v>130746515</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447856</v>
+        <v>447716</v>
       </c>
       <c r="R27" t="n">
-        <v>6784518</v>
+        <v>6784496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,6 +3326,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746515</v>
+        <v>130746518</v>
       </c>
       <c r="B28" t="n">
         <v>8451</v>
@@ -3379,7 +3379,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447716</v>
+        <v>447815</v>
       </c>
       <c r="R28" t="n">
-        <v>6784496</v>
+        <v>6784612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4187,45 +4187,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130746560</v>
+        <v>130746506</v>
       </c>
       <c r="B36" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447685</v>
+        <v>447826</v>
       </c>
       <c r="R36" t="n">
-        <v>6784529</v>
+        <v>6784573</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,6 +4275,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4284,7 +4294,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746565</v>
+        <v>130746560</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4319,10 +4329,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447912</v>
+        <v>447685</v>
       </c>
       <c r="R37" t="n">
-        <v>6784599</v>
+        <v>6784529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,7 +4391,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746561</v>
+        <v>130746565</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4416,10 +4426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447711</v>
+        <v>447912</v>
       </c>
       <c r="R38" t="n">
-        <v>6784677</v>
+        <v>6784599</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,54 +4488,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746506</v>
+        <v>130746561</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447826</v>
+        <v>447711</v>
       </c>
       <c r="R39" t="n">
-        <v>6784573</v>
+        <v>6784677</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4567,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130746495</v>
+        <v>130746563</v>
       </c>
       <c r="B41" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4703,42 +4703,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447746</v>
+        <v>447832</v>
       </c>
       <c r="R41" t="n">
-        <v>6784474</v>
+        <v>6784636</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4797,7 +4789,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746563</v>
+        <v>130746566</v>
       </c>
       <c r="B42" t="n">
         <v>79221</v>
@@ -4832,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447832</v>
+        <v>447949</v>
       </c>
       <c r="R42" t="n">
-        <v>6784636</v>
+        <v>6784550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4894,10 +4886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746566</v>
+        <v>130746495</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4905,34 +4897,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447949</v>
+        <v>447746</v>
       </c>
       <c r="R43" t="n">
-        <v>6784550</v>
+        <v>6784474</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -879,54 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746522</v>
+        <v>130746553</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447866</v>
+        <v>447903</v>
       </c>
       <c r="R4" t="n">
-        <v>6784597</v>
+        <v>6784473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +958,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,45 +976,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130746553</v>
+        <v>130746522</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447903</v>
+        <v>447866</v>
       </c>
       <c r="R5" t="n">
-        <v>6784473</v>
+        <v>6784597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1064,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1497,45 +1497,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746562</v>
+        <v>130746524</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447730</v>
+        <v>447932</v>
       </c>
       <c r="R10" t="n">
-        <v>6784717</v>
+        <v>6784551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,6 +1585,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1594,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746524</v>
+        <v>130746530</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1638,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447932</v>
+        <v>447855</v>
       </c>
       <c r="R11" t="n">
-        <v>6784551</v>
+        <v>6784599</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746530</v>
+        <v>130746519</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1735,7 +1745,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447855</v>
+        <v>447826</v>
       </c>
       <c r="R12" t="n">
-        <v>6784599</v>
+        <v>6784623</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,54 +1818,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746519</v>
+        <v>130746562</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447826</v>
+        <v>447730</v>
       </c>
       <c r="R13" t="n">
-        <v>6784623</v>
+        <v>6784717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,7 +1897,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2012,41 +2012,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746525</v>
+        <v>130746499</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2056,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447933</v>
+        <v>447930</v>
       </c>
       <c r="R15" t="n">
-        <v>6784552</v>
+        <v>6784568</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,7 +2099,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2119,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746570</v>
+        <v>130746500</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,34 +2128,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447857</v>
+        <v>447888</v>
       </c>
       <c r="R16" t="n">
-        <v>6784524</v>
+        <v>6784627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2216,37 +2222,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746554</v>
+        <v>130746525</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2254,10 +2266,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447915</v>
+        <v>447933</v>
       </c>
       <c r="R17" t="n">
-        <v>6784490</v>
+        <v>6784552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746499</v>
+        <v>130746570</v>
       </c>
       <c r="B18" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,42 +2340,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447930</v>
+        <v>447857</v>
       </c>
       <c r="R18" t="n">
-        <v>6784568</v>
+        <v>6784524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130746500</v>
+        <v>130746554</v>
       </c>
       <c r="B19" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,31 +2437,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2465,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447888</v>
+        <v>447915</v>
       </c>
       <c r="R19" t="n">
-        <v>6784627</v>
+        <v>6784490</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,6 +2508,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746531</v>
+        <v>130746546</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>92222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,32 +2538,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2571,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447932</v>
+        <v>447898</v>
       </c>
       <c r="R20" t="n">
-        <v>6784555</v>
+        <v>6784612</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746546</v>
+        <v>130746531</v>
       </c>
       <c r="B21" t="n">
-        <v>92222</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,26 +2639,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447898</v>
+        <v>447932</v>
       </c>
       <c r="R21" t="n">
-        <v>6784612</v>
+        <v>6784555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,45 +2840,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130746556</v>
+        <v>130746510</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447876</v>
+        <v>447718</v>
       </c>
       <c r="R23" t="n">
-        <v>6784529</v>
+        <v>6784441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,6 +2928,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2937,54 +2947,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130746510</v>
+        <v>130746556</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447718</v>
+        <v>447876</v>
       </c>
       <c r="R24" t="n">
-        <v>6784441</v>
+        <v>6784529</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,7 +3026,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3876,45 +3876,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130746555</v>
+        <v>130746523</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447906</v>
+        <v>447940</v>
       </c>
       <c r="R33" t="n">
-        <v>6784505</v>
+        <v>6784589</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3955,6 +3964,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3973,7 +3983,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130746523</v>
+        <v>130746516</v>
       </c>
       <c r="B34" t="n">
         <v>8451</v>
@@ -4017,10 +4027,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447940</v>
+        <v>447725</v>
       </c>
       <c r="R34" t="n">
-        <v>6784589</v>
+        <v>6784696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,54 +4090,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130746516</v>
+        <v>130746555</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447725</v>
+        <v>447906</v>
       </c>
       <c r="R35" t="n">
-        <v>6784696</v>
+        <v>6784505</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,7 +4169,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4187,54 +4187,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130746506</v>
+        <v>130746560</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447826</v>
+        <v>447685</v>
       </c>
       <c r="R36" t="n">
-        <v>6784573</v>
+        <v>6784529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,7 +4266,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4294,7 +4284,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130746560</v>
+        <v>130746565</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4329,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447685</v>
+        <v>447912</v>
       </c>
       <c r="R37" t="n">
-        <v>6784529</v>
+        <v>6784599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,7 +4381,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130746565</v>
+        <v>130746561</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4426,10 +4416,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447912</v>
+        <v>447711</v>
       </c>
       <c r="R38" t="n">
-        <v>6784599</v>
+        <v>6784677</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,45 +4478,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130746561</v>
+        <v>130746506</v>
       </c>
       <c r="B39" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447711</v>
+        <v>447826</v>
       </c>
       <c r="R39" t="n">
-        <v>6784677</v>
+        <v>6784573</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,6 +4566,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5524,7 +5524,7 @@
         <v>131073156</v>
       </c>
       <c r="B49" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>131073209</v>
       </c>
       <c r="B50" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5524,7 +5524,7 @@
         <v>131073156</v>
       </c>
       <c r="B49" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>131073209</v>
       </c>
       <c r="B50" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5524,7 +5524,7 @@
         <v>131073156</v>
       </c>
       <c r="B49" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>131073209</v>
       </c>
       <c r="B50" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5524,7 +5524,7 @@
         <v>131073156</v>
       </c>
       <c r="B49" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>131073209</v>
       </c>
       <c r="B50" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5524,7 +5524,7 @@
         <v>131073156</v>
       </c>
       <c r="B49" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>131073209</v>
       </c>
       <c r="B50" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5738,7 +5738,7 @@
         <v>132153703</v>
       </c>
       <c r="B51" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5959,48 +5959,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132154031</v>
+        <v>132152201</v>
       </c>
       <c r="B53" t="n">
-        <v>97960</v>
+        <v>57945</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447347</v>
+        <v>447506</v>
       </c>
       <c r="R53" t="n">
-        <v>6784550</v>
+        <v>6784286</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6039,7 +6044,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6066,53 +6071,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132152201</v>
+        <v>132154031</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>97963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447506</v>
+        <v>447347</v>
       </c>
       <c r="R54" t="n">
-        <v>6784286</v>
+        <v>6784550</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6290,50 +6290,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132153581</v>
+        <v>132152318</v>
       </c>
       <c r="B56" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447395</v>
+        <v>447512</v>
       </c>
       <c r="R56" t="n">
-        <v>6784505</v>
+        <v>6784322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6375,7 +6370,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6402,45 +6397,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132152318</v>
+        <v>132153581</v>
       </c>
       <c r="B57" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447512</v>
+        <v>447395</v>
       </c>
       <c r="R57" t="n">
-        <v>6784322</v>
+        <v>6784505</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -6290,45 +6290,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132152318</v>
+        <v>132153581</v>
       </c>
       <c r="B56" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447512</v>
+        <v>447395</v>
       </c>
       <c r="R56" t="n">
-        <v>6784322</v>
+        <v>6784505</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6360,7 +6365,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6370,7 +6375,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6397,50 +6402,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132153581</v>
+        <v>132152318</v>
       </c>
       <c r="B57" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447395</v>
+        <v>447512</v>
       </c>
       <c r="R57" t="n">
-        <v>6784505</v>
+        <v>6784322</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5738,7 +5738,7 @@
         <v>132153703</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>132152364</v>
       </c>
       <c r="B52" t="n">
-        <v>57139</v>
+        <v>57140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>132152201</v>
       </c>
       <c r="B53" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>132154031</v>
       </c>
       <c r="B54" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>132152318</v>
       </c>
       <c r="B57" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>132152844</v>
       </c>
       <c r="B59" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>132152630</v>
       </c>
       <c r="B61" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>132153923</v>
       </c>
       <c r="B62" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -6290,50 +6290,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132153581</v>
+        <v>132152318</v>
       </c>
       <c r="B56" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447395</v>
+        <v>447512</v>
       </c>
       <c r="R56" t="n">
-        <v>6784505</v>
+        <v>6784322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6375,7 +6370,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6402,45 +6397,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132152318</v>
+        <v>132153581</v>
       </c>
       <c r="B57" t="n">
-        <v>79319</v>
+        <v>8455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447512</v>
+        <v>447395</v>
       </c>
       <c r="R57" t="n">
-        <v>6784322</v>
+        <v>6784505</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5738,7 +5738,7 @@
         <v>132153703</v>
       </c>
       <c r="B51" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>132152364</v>
       </c>
       <c r="B52" t="n">
-        <v>57140</v>
+        <v>57144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>132152201</v>
       </c>
       <c r="B53" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>132154031</v>
       </c>
       <c r="B54" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>132152318</v>
       </c>
       <c r="B56" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>132152844</v>
       </c>
       <c r="B59" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>132152630</v>
       </c>
       <c r="B61" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>132153923</v>
       </c>
       <c r="B62" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -6290,45 +6290,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132152318</v>
+        <v>132153581</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447512</v>
+        <v>447395</v>
       </c>
       <c r="R56" t="n">
-        <v>6784322</v>
+        <v>6784505</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6360,7 +6365,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6370,7 +6375,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6397,50 +6402,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132153581</v>
+        <v>132152318</v>
       </c>
       <c r="B57" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447395</v>
+        <v>447512</v>
       </c>
       <c r="R57" t="n">
-        <v>6784505</v>
+        <v>6784322</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -6074,7 +6074,7 @@
         <v>132154031</v>
       </c>
       <c r="B54" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6290,50 +6290,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132153581</v>
+        <v>132152318</v>
       </c>
       <c r="B56" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447395</v>
+        <v>447512</v>
       </c>
       <c r="R56" t="n">
-        <v>6784505</v>
+        <v>6784322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6375,7 +6370,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6402,45 +6397,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132152318</v>
+        <v>132153581</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447512</v>
+        <v>447395</v>
       </c>
       <c r="R57" t="n">
-        <v>6784322</v>
+        <v>6784505</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5959,53 +5959,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132152201</v>
+        <v>132154031</v>
       </c>
       <c r="B53" t="n">
-        <v>57950</v>
+        <v>97983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447506</v>
+        <v>447347</v>
       </c>
       <c r="R53" t="n">
-        <v>6784286</v>
+        <v>6784550</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6034,7 +6029,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6044,7 +6039,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6071,48 +6066,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132154031</v>
+        <v>132152201</v>
       </c>
       <c r="B54" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447347</v>
+        <v>447506</v>
       </c>
       <c r="R54" t="n">
-        <v>6784550</v>
+        <v>6784286</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6290,50 +6290,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132153581</v>
+        <v>132152318</v>
       </c>
       <c r="B56" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447395</v>
+        <v>447512</v>
       </c>
       <c r="R56" t="n">
-        <v>6784505</v>
+        <v>6784322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6375,7 +6370,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6402,45 +6397,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132152318</v>
+        <v>132153581</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447512</v>
+        <v>447395</v>
       </c>
       <c r="R57" t="n">
-        <v>6784322</v>
+        <v>6784505</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5738,7 +5738,7 @@
         <v>132153703</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>132152364</v>
       </c>
       <c r="B52" t="n">
-        <v>57144</v>
+        <v>57145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5959,48 +5959,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132154031</v>
+        <v>132152201</v>
       </c>
       <c r="B53" t="n">
-        <v>97983</v>
+        <v>57951</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447347</v>
+        <v>447506</v>
       </c>
       <c r="R53" t="n">
-        <v>6784550</v>
+        <v>6784286</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6039,7 +6044,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6066,53 +6071,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132152201</v>
+        <v>132154031</v>
       </c>
       <c r="B54" t="n">
-        <v>57950</v>
+        <v>97984</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447506</v>
+        <v>447347</v>
       </c>
       <c r="R54" t="n">
-        <v>6784286</v>
+        <v>6784550</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6293,7 +6293,7 @@
         <v>132152318</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>132152844</v>
       </c>
       <c r="B59" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>132152630</v>
       </c>
       <c r="B61" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>132153923</v>
       </c>
       <c r="B62" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5959,53 +5959,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132152201</v>
+        <v>132154031</v>
       </c>
       <c r="B53" t="n">
-        <v>57951</v>
+        <v>97986</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447506</v>
+        <v>447347</v>
       </c>
       <c r="R53" t="n">
-        <v>6784286</v>
+        <v>6784550</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6034,7 +6029,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6044,7 +6039,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6071,48 +6066,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132154031</v>
+        <v>132152201</v>
       </c>
       <c r="B54" t="n">
-        <v>97984</v>
+        <v>57951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447347</v>
+        <v>447506</v>
       </c>
       <c r="R54" t="n">
-        <v>6784550</v>
+        <v>6784286</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -5738,7 +5738,7 @@
         <v>132153703</v>
       </c>
       <c r="B51" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5959,48 +5959,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132154031</v>
+        <v>132152201</v>
       </c>
       <c r="B53" t="n">
-        <v>97986</v>
+        <v>57951</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447347</v>
+        <v>447506</v>
       </c>
       <c r="R53" t="n">
-        <v>6784550</v>
+        <v>6784286</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6039,7 +6044,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6066,53 +6071,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132152201</v>
+        <v>132154031</v>
       </c>
       <c r="B54" t="n">
-        <v>57951</v>
+        <v>97987</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447506</v>
+        <v>447347</v>
       </c>
       <c r="R54" t="n">
-        <v>6784286</v>
+        <v>6784550</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6293,7 +6293,7 @@
         <v>132152318</v>
       </c>
       <c r="B56" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746546</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746551</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746552</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746553</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746554</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746555</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746556</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746557</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746558</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746559</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746560</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746561</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746562</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746563</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746564</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746565</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746566</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746567</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746569</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746570</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131073156</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131073209</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2941,6 +3056,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152318</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3048,6 +3168,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132153703</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3153,6 +3278,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128786501</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3258,6 +3388,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746493</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3363,6 +3498,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746495</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3468,6 +3608,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746496</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746497</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3678,6 +3828,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746498</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3783,6 +3938,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746499</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3888,6 +4048,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746500</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4000,6 +4165,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152201</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4112,6 +4282,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152630</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4224,6 +4399,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152844</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4336,6 +4516,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132153923</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4448,6 +4633,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154128</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4565,6 +4755,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152364</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4670,6 +4865,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746490</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4777,6 +4977,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128786505</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4884,6 +5089,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746501</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4991,6 +5201,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746502</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5098,6 +5313,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746503</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5205,6 +5425,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746504</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5312,6 +5537,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746505</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5419,6 +5649,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746506</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5526,6 +5761,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746507</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5633,6 +5873,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746508</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5740,6 +5985,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746510</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5847,6 +6097,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746511</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5954,6 +6209,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746512</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6061,6 +6321,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746513</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6168,6 +6433,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746515</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6275,6 +6545,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746516</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6382,6 +6657,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746517</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6489,6 +6769,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746518</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6596,6 +6881,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746519</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6703,6 +6993,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746520</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6810,6 +7105,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746521</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6917,6 +7217,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746522</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7024,6 +7329,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746523</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7131,6 +7441,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746524</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7238,6 +7553,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746525</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7345,6 +7665,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746526</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7452,6 +7777,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746528</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7559,6 +7889,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746530</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7666,6 +8001,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746531</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7778,6 +8118,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131073028</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7890,6 +8235,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152152</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8002,6 +8352,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152776</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8114,6 +8469,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152920</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8226,6 +8586,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132153492</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8338,6 +8703,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132153581</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8450,6 +8820,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154197</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8557,6 +8932,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154031</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8664,8 +9044,91 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132152092</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ77"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130746546</v>
+        <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>93341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Dlr</t>
+          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447898</v>
+        <v>447710</v>
       </c>
       <c r="R2" t="n">
-        <v>6784612</v>
+        <v>6784425</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,51 +786,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746546</t>
+          <t>https://artportalen.se/Sighting/135987196</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130746551</v>
+        <v>130746546</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447928</v>
+        <v>447898</v>
       </c>
       <c r="R3" t="n">
-        <v>6784508</v>
+        <v>6784612</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,13 +892,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746551</t>
+          <t>https://artportalen.se/Sighting/130746546</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130746552</v>
+        <v>130746551</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -923,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447914</v>
+        <v>447928</v>
       </c>
       <c r="R4" t="n">
-        <v>6784497</v>
+        <v>6784508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,13 +994,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746552</t>
+          <t>https://artportalen.se/Sighting/130746551</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130746553</v>
+        <v>130746552</v>
       </c>
       <c r="B5" t="n">
         <v>79327</v>
@@ -1025,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447903</v>
+        <v>447914</v>
       </c>
       <c r="R5" t="n">
-        <v>6784473</v>
+        <v>6784497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,13 +1096,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746553</t>
+          <t>https://artportalen.se/Sighting/130746552</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130746554</v>
+        <v>130746553</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1121,19 +1131,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447915</v>
+        <v>447903</v>
       </c>
       <c r="R6" t="n">
-        <v>6784490</v>
+        <v>6784473</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1181,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1192,13 +1198,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746554</t>
+          <t>https://artportalen.se/Sighting/130746553</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130746555</v>
+        <v>130746554</v>
       </c>
       <c r="B7" t="n">
         <v>79327</v>
@@ -1227,16 +1233,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447906</v>
+        <v>447915</v>
       </c>
       <c r="R7" t="n">
-        <v>6784505</v>
+        <v>6784490</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,6 +1286,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1294,13 +1304,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746555</t>
+          <t>https://artportalen.se/Sighting/130746554</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130746556</v>
+        <v>130746555</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1335,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447876</v>
+        <v>447906</v>
       </c>
       <c r="R8" t="n">
-        <v>6784529</v>
+        <v>6784505</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,13 +1406,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746556</t>
+          <t>https://artportalen.se/Sighting/130746555</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130746557</v>
+        <v>130746556</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1437,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447768</v>
+        <v>447876</v>
       </c>
       <c r="R9" t="n">
-        <v>6784456</v>
+        <v>6784529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,13 +1508,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746557</t>
+          <t>https://artportalen.se/Sighting/130746556</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130746558</v>
+        <v>130746557</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1539,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447718</v>
+        <v>447768</v>
       </c>
       <c r="R10" t="n">
-        <v>6784468</v>
+        <v>6784456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,13 +1610,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746558</t>
+          <t>https://artportalen.se/Sighting/130746557</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130746559</v>
+        <v>130746558</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1641,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447697</v>
+        <v>447718</v>
       </c>
       <c r="R11" t="n">
-        <v>6784479</v>
+        <v>6784468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,13 +1712,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746559</t>
+          <t>https://artportalen.se/Sighting/130746558</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130746560</v>
+        <v>130746559</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1743,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447685</v>
+        <v>447697</v>
       </c>
       <c r="R12" t="n">
-        <v>6784529</v>
+        <v>6784479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,13 +1814,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746560</t>
+          <t>https://artportalen.se/Sighting/130746559</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130746561</v>
+        <v>130746560</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1845,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447711</v>
+        <v>447685</v>
       </c>
       <c r="R13" t="n">
-        <v>6784677</v>
+        <v>6784529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,13 +1916,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746561</t>
+          <t>https://artportalen.se/Sighting/130746560</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130746562</v>
+        <v>130746561</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1947,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447730</v>
+        <v>447711</v>
       </c>
       <c r="R14" t="n">
-        <v>6784717</v>
+        <v>6784677</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,13 +2018,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746562</t>
+          <t>https://artportalen.se/Sighting/130746561</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130746563</v>
+        <v>130746562</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2049,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447832</v>
+        <v>447730</v>
       </c>
       <c r="R15" t="n">
-        <v>6784636</v>
+        <v>6784717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,13 +2120,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746563</t>
+          <t>https://artportalen.se/Sighting/130746562</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130746564</v>
+        <v>130746563</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2151,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447866</v>
+        <v>447832</v>
       </c>
       <c r="R16" t="n">
-        <v>6784648</v>
+        <v>6784636</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2212,13 +2222,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746564</t>
+          <t>https://artportalen.se/Sighting/130746563</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130746565</v>
+        <v>130746564</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2253,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447912</v>
+        <v>447866</v>
       </c>
       <c r="R17" t="n">
-        <v>6784599</v>
+        <v>6784648</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,13 +2324,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746565</t>
+          <t>https://artportalen.se/Sighting/130746564</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130746566</v>
+        <v>130746565</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2355,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447949</v>
+        <v>447912</v>
       </c>
       <c r="R18" t="n">
-        <v>6784550</v>
+        <v>6784599</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2416,13 +2426,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746566</t>
+          <t>https://artportalen.se/Sighting/130746565</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130746567</v>
+        <v>130746566</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2457,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448010</v>
+        <v>447949</v>
       </c>
       <c r="R19" t="n">
-        <v>6784537</v>
+        <v>6784550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2518,13 +2528,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746567</t>
+          <t>https://artportalen.se/Sighting/130746566</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130746569</v>
+        <v>130746567</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2559,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447856</v>
+        <v>448010</v>
       </c>
       <c r="R20" t="n">
-        <v>6784518</v>
+        <v>6784537</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,13 +2630,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746569</t>
+          <t>https://artportalen.se/Sighting/130746567</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130746570</v>
+        <v>130746569</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2661,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447857</v>
+        <v>447856</v>
       </c>
       <c r="R21" t="n">
-        <v>6784524</v>
+        <v>6784518</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,13 +2732,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746570</t>
+          <t>https://artportalen.se/Sighting/130746569</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131073156</v>
+        <v>130746570</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2759,14 +2769,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
+          <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447572</v>
+        <v>447857</v>
       </c>
       <c r="R22" t="n">
-        <v>6784666</v>
+        <v>6784524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2793,22 +2803,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2834,13 +2834,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131073156</t>
+          <t>https://artportalen.se/Sighting/130746570</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131073209</v>
+        <v>131073156</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447552</v>
+        <v>447572</v>
       </c>
       <c r="R23" t="n">
-        <v>6784648</v>
+        <v>6784666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2946,16 +2946,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131073209</t>
+          <t>https://artportalen.se/Sighting/131073156</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132152318</v>
+        <v>131073209</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447512</v>
+        <v>447552</v>
       </c>
       <c r="R24" t="n">
-        <v>6784322</v>
+        <v>6784648</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3017,22 +3017,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3058,13 +3058,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152318</t>
+          <t>https://artportalen.se/Sighting/131073209</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132153703</v>
+        <v>132152318</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447374</v>
+        <v>447512</v>
       </c>
       <c r="R25" t="n">
-        <v>6784519</v>
+        <v>6784322</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3170,59 +3170,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132153703</t>
+          <t>https://artportalen.se/Sighting/132152318</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128786501</v>
+        <v>132153703</v>
       </c>
       <c r="B26" t="n">
-        <v>57950</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hållbergsvägen, Dlr</t>
+          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447785</v>
+        <v>447374</v>
       </c>
       <c r="R26" t="n">
-        <v>6784411</v>
+        <v>6784519</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,12 +3241,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,13 +3282,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128786501</t>
+          <t>https://artportalen.se/Sighting/132153703</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130746493</v>
+        <v>128786501</v>
       </c>
       <c r="B27" t="n">
         <v>57950</v>
@@ -3325,14 +3327,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Dlr</t>
+          <t>Hållbergsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447766</v>
+        <v>447785</v>
       </c>
       <c r="R27" t="n">
-        <v>6784433</v>
+        <v>6784411</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3359,12 +3361,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3390,13 +3392,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746493</t>
+          <t>https://artportalen.se/Sighting/128786501</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130746495</v>
+        <v>130746493</v>
       </c>
       <c r="B28" t="n">
         <v>57950</v>
@@ -3429,7 +3431,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3439,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447746</v>
+        <v>447766</v>
       </c>
       <c r="R28" t="n">
-        <v>6784474</v>
+        <v>6784433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,13 +3502,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746495</t>
+          <t>https://artportalen.se/Sighting/130746493</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130746496</v>
+        <v>130746495</v>
       </c>
       <c r="B29" t="n">
         <v>57950</v>
@@ -3549,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447817</v>
+        <v>447746</v>
       </c>
       <c r="R29" t="n">
-        <v>6784636</v>
+        <v>6784474</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,13 +3612,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746496</t>
+          <t>https://artportalen.se/Sighting/130746495</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130746497</v>
+        <v>130746496</v>
       </c>
       <c r="B30" t="n">
         <v>57950</v>
@@ -3659,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447838</v>
+        <v>447817</v>
       </c>
       <c r="R30" t="n">
-        <v>6784644</v>
+        <v>6784636</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,13 +3722,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746497</t>
+          <t>https://artportalen.se/Sighting/130746496</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130746498</v>
+        <v>130746497</v>
       </c>
       <c r="B31" t="n">
         <v>57950</v>
@@ -3769,10 +3771,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447886</v>
+        <v>447838</v>
       </c>
       <c r="R31" t="n">
-        <v>6784627</v>
+        <v>6784644</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,13 +3832,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746498</t>
+          <t>https://artportalen.se/Sighting/130746497</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130746499</v>
+        <v>130746498</v>
       </c>
       <c r="B32" t="n">
         <v>57950</v>
@@ -3869,7 +3871,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3879,10 +3881,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447930</v>
+        <v>447886</v>
       </c>
       <c r="R32" t="n">
-        <v>6784568</v>
+        <v>6784627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,13 +3942,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746499</t>
+          <t>https://artportalen.se/Sighting/130746498</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130746500</v>
+        <v>130746499</v>
       </c>
       <c r="B33" t="n">
         <v>57950</v>
@@ -3989,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447888</v>
+        <v>447930</v>
       </c>
       <c r="R33" t="n">
-        <v>6784627</v>
+        <v>6784568</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,16 +4052,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746500</t>
+          <t>https://artportalen.se/Sighting/130746499</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132152201</v>
+        <v>130746500</v>
       </c>
       <c r="B34" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,21 +4087,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
+          <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447506</v>
+        <v>447888</v>
       </c>
       <c r="R34" t="n">
-        <v>6784286</v>
+        <v>6784627</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,22 +4131,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,13 +4162,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152201</t>
+          <t>https://artportalen.se/Sighting/130746500</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132152630</v>
+        <v>132152201</v>
       </c>
       <c r="B35" t="n">
         <v>57972</v>
@@ -4204,7 +4199,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4213,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447512</v>
+        <v>447506</v>
       </c>
       <c r="R35" t="n">
-        <v>6784322</v>
+        <v>6784286</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,7 +4243,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4258,7 +4253,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4284,13 +4279,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152630</t>
+          <t>https://artportalen.se/Sighting/132152201</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132152844</v>
+        <v>132152630</v>
       </c>
       <c r="B36" t="n">
         <v>57972</v>
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447481</v>
+        <v>447512</v>
       </c>
       <c r="R36" t="n">
-        <v>6784397</v>
+        <v>6784322</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4360,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4375,7 +4370,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4401,13 +4396,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152844</t>
+          <t>https://artportalen.se/Sighting/132152630</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132153923</v>
+        <v>132152844</v>
       </c>
       <c r="B37" t="n">
         <v>57972</v>
@@ -4438,7 +4433,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447355</v>
+        <v>447481</v>
       </c>
       <c r="R37" t="n">
-        <v>6784538</v>
+        <v>6784397</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,7 +4477,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4492,7 +4487,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4518,13 +4513,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132153923</t>
+          <t>https://artportalen.se/Sighting/132152844</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132154128</v>
+        <v>132153923</v>
       </c>
       <c r="B38" t="n">
         <v>57972</v>
@@ -4555,7 +4550,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4564,13 +4559,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447327</v>
+        <v>447355</v>
       </c>
       <c r="R38" t="n">
-        <v>6784585</v>
+        <v>6784538</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4599,7 +4594,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4609,7 +4604,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4635,16 +4630,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132154128</t>
+          <t>https://artportalen.se/Sighting/132153923</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132152364</v>
+        <v>132154128</v>
       </c>
       <c r="B39" t="n">
-        <v>57165</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4652,16 +4647,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4670,14 +4665,9 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4686,13 +4676,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447512</v>
+        <v>447327</v>
       </c>
       <c r="R39" t="n">
-        <v>6784322</v>
+        <v>6784585</v>
       </c>
       <c r="S39" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4721,7 +4711,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4731,7 +4721,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4757,62 +4747,64 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152364</t>
+          <t>https://artportalen.se/Sighting/132154128</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130746490</v>
+        <v>132152364</v>
       </c>
       <c r="B40" t="n">
-        <v>58114</v>
+        <v>57165</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Dlr</t>
+          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447888</v>
+        <v>447512</v>
       </c>
       <c r="R40" t="n">
-        <v>6784627</v>
+        <v>6784322</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4836,12 +4828,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,60 +4869,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746490</t>
+          <t>https://artportalen.se/Sighting/132152364</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128786505</v>
+        <v>130746490</v>
       </c>
       <c r="B41" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hållbergsvägen, Dlr</t>
+          <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447762</v>
+        <v>447888</v>
       </c>
       <c r="R41" t="n">
-        <v>6784437</v>
+        <v>6784627</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,12 +4948,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4961,7 +4962,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4979,13 +4979,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128786505</t>
+          <t>https://artportalen.se/Sighting/130746490</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130746501</v>
+        <v>128786505</v>
       </c>
       <c r="B42" t="n">
         <v>8455</v>
@@ -5025,14 +5025,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Dlr</t>
+          <t>Hållbergsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447967</v>
+        <v>447762</v>
       </c>
       <c r="R42" t="n">
-        <v>6784475</v>
+        <v>6784437</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5091,13 +5091,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746501</t>
+          <t>https://artportalen.se/Sighting/128786505</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746502</v>
+        <v>130746501</v>
       </c>
       <c r="B43" t="n">
         <v>8455</v>
@@ -5131,7 +5131,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447975</v>
+        <v>447967</v>
       </c>
       <c r="R43" t="n">
-        <v>6784493</v>
+        <v>6784475</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5203,13 +5203,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746502</t>
+          <t>https://artportalen.se/Sighting/130746501</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746503</v>
+        <v>130746502</v>
       </c>
       <c r="B44" t="n">
         <v>8455</v>
@@ -5243,7 +5243,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447933</v>
+        <v>447975</v>
       </c>
       <c r="R44" t="n">
-        <v>6784497</v>
+        <v>6784493</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5315,13 +5315,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746503</t>
+          <t>https://artportalen.se/Sighting/130746502</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130746504</v>
+        <v>130746503</v>
       </c>
       <c r="B45" t="n">
         <v>8455</v>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447917</v>
+        <v>447933</v>
       </c>
       <c r="R45" t="n">
-        <v>6784459</v>
+        <v>6784497</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5427,13 +5427,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746504</t>
+          <t>https://artportalen.se/Sighting/130746503</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130746505</v>
+        <v>130746504</v>
       </c>
       <c r="B46" t="n">
         <v>8455</v>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447906</v>
+        <v>447917</v>
       </c>
       <c r="R46" t="n">
-        <v>6784476</v>
+        <v>6784459</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5539,13 +5539,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746505</t>
+          <t>https://artportalen.se/Sighting/130746504</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130746506</v>
+        <v>130746505</v>
       </c>
       <c r="B47" t="n">
         <v>8455</v>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447826</v>
+        <v>447906</v>
       </c>
       <c r="R47" t="n">
-        <v>6784573</v>
+        <v>6784476</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5651,13 +5651,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746506</t>
+          <t>https://artportalen.se/Sighting/130746505</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130746507</v>
+        <v>130746506</v>
       </c>
       <c r="B48" t="n">
         <v>8455</v>
@@ -5704,7 +5704,7 @@
         <v>447826</v>
       </c>
       <c r="R48" t="n">
-        <v>6784536</v>
+        <v>6784573</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5763,13 +5763,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746507</t>
+          <t>https://artportalen.se/Sighting/130746506</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130746508</v>
+        <v>130746507</v>
       </c>
       <c r="B49" t="n">
         <v>8455</v>
@@ -5813,10 +5813,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447816</v>
+        <v>447826</v>
       </c>
       <c r="R49" t="n">
-        <v>6784561</v>
+        <v>6784536</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5875,13 +5875,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746508</t>
+          <t>https://artportalen.se/Sighting/130746507</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130746510</v>
+        <v>130746508</v>
       </c>
       <c r="B50" t="n">
         <v>8455</v>
@@ -5925,10 +5925,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447718</v>
+        <v>447816</v>
       </c>
       <c r="R50" t="n">
-        <v>6784441</v>
+        <v>6784561</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5987,13 +5987,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746510</t>
+          <t>https://artportalen.se/Sighting/130746508</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130746511</v>
+        <v>130746510</v>
       </c>
       <c r="B51" t="n">
         <v>8455</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447748</v>
+        <v>447718</v>
       </c>
       <c r="R51" t="n">
-        <v>6784472</v>
+        <v>6784441</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6099,13 +6099,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746511</t>
+          <t>https://artportalen.se/Sighting/130746510</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130746512</v>
+        <v>130746511</v>
       </c>
       <c r="B52" t="n">
         <v>8455</v>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447746</v>
+        <v>447748</v>
       </c>
       <c r="R52" t="n">
-        <v>6784500</v>
+        <v>6784472</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6211,13 +6211,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746512</t>
+          <t>https://artportalen.se/Sighting/130746511</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130746513</v>
+        <v>130746512</v>
       </c>
       <c r="B53" t="n">
         <v>8455</v>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447735</v>
+        <v>447746</v>
       </c>
       <c r="R53" t="n">
-        <v>6784515</v>
+        <v>6784500</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6323,13 +6323,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746513</t>
+          <t>https://artportalen.se/Sighting/130746512</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130746515</v>
+        <v>130746513</v>
       </c>
       <c r="B54" t="n">
         <v>8455</v>
@@ -6363,7 +6363,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447716</v>
+        <v>447735</v>
       </c>
       <c r="R54" t="n">
-        <v>6784496</v>
+        <v>6784515</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6435,13 +6435,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746515</t>
+          <t>https://artportalen.se/Sighting/130746513</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130746516</v>
+        <v>130746515</v>
       </c>
       <c r="B55" t="n">
         <v>8455</v>
@@ -6475,7 +6475,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447725</v>
+        <v>447716</v>
       </c>
       <c r="R55" t="n">
-        <v>6784696</v>
+        <v>6784496</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6547,13 +6547,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746516</t>
+          <t>https://artportalen.se/Sighting/130746515</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130746517</v>
+        <v>130746516</v>
       </c>
       <c r="B56" t="n">
         <v>8455</v>
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447805</v>
+        <v>447725</v>
       </c>
       <c r="R56" t="n">
-        <v>6784562</v>
+        <v>6784696</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6659,13 +6659,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746517</t>
+          <t>https://artportalen.se/Sighting/130746516</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130746518</v>
+        <v>130746517</v>
       </c>
       <c r="B57" t="n">
         <v>8455</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447815</v>
+        <v>447805</v>
       </c>
       <c r="R57" t="n">
-        <v>6784612</v>
+        <v>6784562</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6771,13 +6771,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746518</t>
+          <t>https://artportalen.se/Sighting/130746517</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130746519</v>
+        <v>130746518</v>
       </c>
       <c r="B58" t="n">
         <v>8455</v>
@@ -6811,7 +6811,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447826</v>
+        <v>447815</v>
       </c>
       <c r="R58" t="n">
-        <v>6784623</v>
+        <v>6784612</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6883,13 +6883,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746519</t>
+          <t>https://artportalen.se/Sighting/130746518</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130746520</v>
+        <v>130746519</v>
       </c>
       <c r="B59" t="n">
         <v>8455</v>
@@ -6923,7 +6923,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447846</v>
+        <v>447826</v>
       </c>
       <c r="R59" t="n">
-        <v>6784643</v>
+        <v>6784623</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6995,13 +6995,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746520</t>
+          <t>https://artportalen.se/Sighting/130746519</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130746521</v>
+        <v>130746520</v>
       </c>
       <c r="B60" t="n">
         <v>8455</v>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447834</v>
+        <v>447846</v>
       </c>
       <c r="R60" t="n">
-        <v>6784604</v>
+        <v>6784643</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7107,13 +7107,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746521</t>
+          <t>https://artportalen.se/Sighting/130746520</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130746522</v>
+        <v>130746521</v>
       </c>
       <c r="B61" t="n">
         <v>8455</v>
@@ -7147,7 +7147,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447866</v>
+        <v>447834</v>
       </c>
       <c r="R61" t="n">
-        <v>6784597</v>
+        <v>6784604</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7219,13 +7219,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746522</t>
+          <t>https://artportalen.se/Sighting/130746521</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130746523</v>
+        <v>130746522</v>
       </c>
       <c r="B62" t="n">
         <v>8455</v>
@@ -7259,7 +7259,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447940</v>
+        <v>447866</v>
       </c>
       <c r="R62" t="n">
-        <v>6784589</v>
+        <v>6784597</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7331,13 +7331,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746523</t>
+          <t>https://artportalen.se/Sighting/130746522</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130746524</v>
+        <v>130746523</v>
       </c>
       <c r="B63" t="n">
         <v>8455</v>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447932</v>
+        <v>447940</v>
       </c>
       <c r="R63" t="n">
-        <v>6784551</v>
+        <v>6784589</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7443,13 +7443,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746524</t>
+          <t>https://artportalen.se/Sighting/130746523</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130746525</v>
+        <v>130746524</v>
       </c>
       <c r="B64" t="n">
         <v>8455</v>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447933</v>
+        <v>447932</v>
       </c>
       <c r="R64" t="n">
-        <v>6784552</v>
+        <v>6784551</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7555,13 +7555,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746525</t>
+          <t>https://artportalen.se/Sighting/130746524</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130746526</v>
+        <v>130746525</v>
       </c>
       <c r="B65" t="n">
         <v>8455</v>
@@ -7595,7 +7595,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447950</v>
+        <v>447933</v>
       </c>
       <c r="R65" t="n">
-        <v>6784549</v>
+        <v>6784552</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7667,13 +7667,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746526</t>
+          <t>https://artportalen.se/Sighting/130746525</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130746528</v>
+        <v>130746526</v>
       </c>
       <c r="B66" t="n">
         <v>8455</v>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447952</v>
+        <v>447950</v>
       </c>
       <c r="R66" t="n">
-        <v>6784545</v>
+        <v>6784549</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7779,13 +7779,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746528</t>
+          <t>https://artportalen.se/Sighting/130746526</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130746530</v>
+        <v>130746528</v>
       </c>
       <c r="B67" t="n">
         <v>8455</v>
@@ -7819,7 +7819,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447855</v>
+        <v>447952</v>
       </c>
       <c r="R67" t="n">
-        <v>6784599</v>
+        <v>6784545</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7891,13 +7891,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746530</t>
+          <t>https://artportalen.se/Sighting/130746528</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130746531</v>
+        <v>130746530</v>
       </c>
       <c r="B68" t="n">
         <v>8455</v>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447932</v>
+        <v>447855</v>
       </c>
       <c r="R68" t="n">
-        <v>6784555</v>
+        <v>6784599</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8003,13 +8003,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746531</t>
+          <t>https://artportalen.se/Sighting/130746530</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131073028</v>
+        <v>130746531</v>
       </c>
       <c r="B69" t="n">
         <v>8455</v>
@@ -8038,21 +8038,25 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
+          <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447573</v>
+        <v>447932</v>
       </c>
       <c r="R69" t="n">
-        <v>6784308</v>
+        <v>6784555</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8079,22 +8083,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8103,6 +8097,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8120,16 +8115,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131073028</t>
+          <t>https://artportalen.se/Sighting/130746531</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132152152</v>
+        <v>131073028</v>
       </c>
       <c r="B70" t="n">
-        <v>8460</v>
+        <v>8455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8157,19 +8152,19 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
+          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447524</v>
+        <v>447573</v>
       </c>
       <c r="R70" t="n">
-        <v>6784261</v>
+        <v>6784308</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8196,22 +8191,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8237,13 +8232,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152152</t>
+          <t>https://artportalen.se/Sighting/131073028</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132152776</v>
+        <v>132152152</v>
       </c>
       <c r="B71" t="n">
         <v>8460</v>
@@ -8279,14 +8274,14 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
+          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447492</v>
+        <v>447524</v>
       </c>
       <c r="R71" t="n">
-        <v>6784359</v>
+        <v>6784261</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8318,7 +8313,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8328,7 +8323,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8354,13 +8349,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152776</t>
+          <t>https://artportalen.se/Sighting/132152152</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132152920</v>
+        <v>132152776</v>
       </c>
       <c r="B72" t="n">
         <v>8460</v>
@@ -8400,10 +8395,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447481</v>
+        <v>447492</v>
       </c>
       <c r="R72" t="n">
-        <v>6784397</v>
+        <v>6784359</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8435,7 +8430,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8445,7 +8440,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8471,13 +8466,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152920</t>
+          <t>https://artportalen.se/Sighting/132152776</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132153492</v>
+        <v>132152920</v>
       </c>
       <c r="B73" t="n">
         <v>8460</v>
@@ -8517,10 +8512,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447376</v>
+        <v>447481</v>
       </c>
       <c r="R73" t="n">
-        <v>6784477</v>
+        <v>6784397</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8552,7 +8547,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8562,7 +8557,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8588,13 +8583,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132153492</t>
+          <t>https://artportalen.se/Sighting/132152920</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132153581</v>
+        <v>132153492</v>
       </c>
       <c r="B74" t="n">
         <v>8460</v>
@@ -8634,10 +8629,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447395</v>
+        <v>447376</v>
       </c>
       <c r="R74" t="n">
-        <v>6784505</v>
+        <v>6784477</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8669,7 +8664,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8679,7 +8674,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8705,13 +8700,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132153581</t>
+          <t>https://artportalen.se/Sighting/132153492</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132154197</v>
+        <v>132153581</v>
       </c>
       <c r="B75" t="n">
         <v>8460</v>
@@ -8751,13 +8746,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447308</v>
+        <v>447395</v>
       </c>
       <c r="R75" t="n">
-        <v>6784594</v>
+        <v>6784505</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8786,7 +8781,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8796,7 +8791,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8822,16 +8817,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132154197</t>
+          <t>https://artportalen.se/Sighting/132153581</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132154031</v>
+        <v>132154197</v>
       </c>
       <c r="B76" t="n">
-        <v>98060</v>
+        <v>8460</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8839,34 +8834,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447347</v>
+        <v>447308</v>
       </c>
       <c r="R76" t="n">
-        <v>6784550</v>
+        <v>6784594</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8934,54 +8934,54 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132154031</t>
+          <t>https://artportalen.se/Sighting/132154197</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132152092</v>
+        <v>132154031</v>
       </c>
       <c r="B77" t="n">
-        <v>79374</v>
+        <v>98060</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230405</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
+          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447535</v>
+        <v>447347</v>
       </c>
       <c r="R77" t="n">
-        <v>6784263</v>
+        <v>6784550</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9045,6 +9045,118 @@
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154031</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132152092</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79374</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>447535</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6784263</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132152092</t>
         </is>
@@ -9128,6 +9240,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135987196</v>
       </c>
       <c r="B2" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
